--- a/automation/reports/Excel/Summary_Report.xlsx
+++ b/automation/reports/Excel/Summary_Report.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.88</v>
+        <v>5.11</v>
       </c>
     </row>
   </sheetData>
